--- a/C/Project/ATM_Sim/Doc/Requirement.xlsx
+++ b/C/Project/ATM_Sim/Doc/Requirement.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Embedded\C\Project\ATM_Sim\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Jira project\Embedded\C\Project\ATM_Sim\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67620170-457A-47F5-9354-6ACE4B6C92CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF789CA-DEA9-4066-8EA1-F7E2077DC1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>SYS</t>
   </si>
@@ -66,16 +66,52 @@
   <si>
     <t>Source code based on C language,
 without UI support capability</t>
+  </si>
+  <si>
+    <t>SYS_003</t>
+  </si>
+  <si>
+    <t>SYS_004</t>
+  </si>
+  <si>
+    <t>SYS_005</t>
+  </si>
+  <si>
+    <t>SYS_006</t>
+  </si>
+  <si>
+    <t>SYS_007</t>
+  </si>
+  <si>
+    <t>ATM appllication should have PIN code</t>
+  </si>
+  <si>
+    <t>ATM appllication should balance view</t>
+  </si>
+  <si>
+    <t>ATM appllication should withdraw money</t>
+  </si>
+  <si>
+    <t>ATM appllication should transfer money</t>
+  </si>
+  <si>
+    <t>ATM appllication should logged in account</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -386,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
@@ -428,7 +464,48 @@
         <v>12</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/C/Project/ATM_Sim/Doc/Requirement.xlsx
+++ b/C/Project/ATM_Sim/Doc/Requirement.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Jira project\Embedded\C\Project\ATM_Sim\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Embedded\C\Project\ATM_Sim\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF789CA-DEA9-4066-8EA1-F7E2077DC1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67620170-457A-47F5-9354-6ACE4B6C92CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>SYS</t>
   </si>
@@ -67,51 +67,15 @@
     <t>Source code based on C language,
 without UI support capability</t>
   </si>
-  <si>
-    <t>SYS_003</t>
-  </si>
-  <si>
-    <t>SYS_004</t>
-  </si>
-  <si>
-    <t>SYS_005</t>
-  </si>
-  <si>
-    <t>SYS_006</t>
-  </si>
-  <si>
-    <t>SYS_007</t>
-  </si>
-  <si>
-    <t>ATM appllication should have PIN code</t>
-  </si>
-  <si>
-    <t>ATM appllication should balance view</t>
-  </si>
-  <si>
-    <t>ATM appllication should withdraw money</t>
-  </si>
-  <si>
-    <t>ATM appllication should transfer money</t>
-  </si>
-  <si>
-    <t>ATM appllication should logged in account</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -422,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
@@ -464,48 +428,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/C/Project/ATM_Sim/Doc/Requirement.xlsx
+++ b/C/Project/ATM_Sim/Doc/Requirement.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Embedded\C\Project\ATM_Sim\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Jira project\Embedded\C\Project\ATM_Sim\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67620170-457A-47F5-9354-6ACE4B6C92CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBC436F-E34A-4490-A031-E47AFBF80BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>SYS</t>
   </si>
@@ -64,18 +64,92 @@
     <t>ATM application should be run console, not using UI</t>
   </si>
   <si>
-    <t>Source code based on C language,
-without UI support capability</t>
+    <t>SYS_003</t>
+  </si>
+  <si>
+    <t>SYS_004</t>
+  </si>
+  <si>
+    <t>Source code based on C language, without UI support capability</t>
+  </si>
+  <si>
+    <t>ATM application will allow user to select the cash withdrawl function</t>
+  </si>
+  <si>
+    <t>ATM application will allow user enter or select the amount of cash to withdraw</t>
+  </si>
+  <si>
+    <t>ATM application will verify that the withdrawl amount does not exceed the available account balance</t>
+  </si>
+  <si>
+    <t>ATM application will dispense the request amount when the withdrawl transaction is successful</t>
+  </si>
+  <si>
+    <t>ATM application will update the account balance after a successful cash withdrawl</t>
+  </si>
+  <si>
+    <t>ATM application will display an error message when the withdrawl amount exceeds the available account balance</t>
+  </si>
+  <si>
+    <t>ATM application will display the current transaction status after each withdrawl operation</t>
+  </si>
+  <si>
+    <t>SYS_005</t>
+  </si>
+  <si>
+    <t>SYS_006</t>
+  </si>
+  <si>
+    <t>SYS_007</t>
+  </si>
+  <si>
+    <t>SYS_008</t>
+  </si>
+  <si>
+    <t>SYS_009</t>
+  </si>
+  <si>
+    <t>ATM application will allow user to cancel the withdrawl transaction before cash is dispensed</t>
+  </si>
+  <si>
+    <t>ATM application will display the result of the withdrawll transaction after processing</t>
+  </si>
+  <si>
+    <t>SYS_010</t>
+  </si>
+  <si>
+    <t>SYS_011</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -101,10 +175,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -386,49 +475,139 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="73.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.36328125" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.90625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.36328125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/C/Project/ATM_Sim/Doc/Requirement.xlsx
+++ b/C/Project/ATM_Sim/Doc/Requirement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Jira project\Embedded\C\Project\ATM_Sim\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBC436F-E34A-4490-A031-E47AFBF80BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635EF8C0-55AA-43AE-A08C-9CF0B7B6857C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="214">
   <si>
     <t>SYS</t>
   </si>
@@ -119,13 +119,573 @@
   </si>
   <si>
     <t>SYS_011</t>
+  </si>
+  <si>
+    <t>LOG_001</t>
+  </si>
+  <si>
+    <t>PIN Authentication</t>
+  </si>
+  <si>
+    <t>LOG_002</t>
+  </si>
+  <si>
+    <t>LOG_003</t>
+  </si>
+  <si>
+    <t>Successful authentication</t>
+  </si>
+  <si>
+    <t>LOG_004</t>
+  </si>
+  <si>
+    <t>Failed authentication</t>
+  </si>
+  <si>
+    <t>LOG_005</t>
+  </si>
+  <si>
+    <t>Retry</t>
+  </si>
+  <si>
+    <t>LOG_006</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>LOG_007</t>
+  </si>
+  <si>
+    <t>ATM application will require the user to enter a PIN after inserting a valid card</t>
+  </si>
+  <si>
+    <t>ATM application will verify the entered PIN against the PIN associated with the user's account</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to retry PIN entry after an incorrect PIN</t>
+  </si>
+  <si>
+    <t>ATM application will terminate the session or block further authentication attempts when the maximum number of incorrect PIN attempts is reached</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to access ATM services when the PIN is correct</t>
+  </si>
+  <si>
+    <t>ATM application will reject the login attempt when the PIN is incorrect</t>
+  </si>
+  <si>
+    <t>CI_001</t>
+  </si>
+  <si>
+    <t>CI_002</t>
+  </si>
+  <si>
+    <t>CI_003</t>
+  </si>
+  <si>
+    <t>CI_004</t>
+  </si>
+  <si>
+    <t>CI_005</t>
+  </si>
+  <si>
+    <t>ATM  application will not display the entered PIN in plain text on the console</t>
+  </si>
+  <si>
+    <t>ATM application will simulate card insertion when the user starts a transaction</t>
+  </si>
+  <si>
+    <t>ATM application will validate the simulated card before proceeding</t>
+  </si>
+  <si>
+    <t>ATM application will reject an invalid or unsupported card</t>
+  </si>
+  <si>
+    <t>ATM application will proceed to PIN authentication after a valid card is detected</t>
+  </si>
+  <si>
+    <t>ATM  application will simulate returning the card when the transaction is completed or cancelled</t>
+  </si>
+  <si>
+    <t>BI_001</t>
+  </si>
+  <si>
+    <t>BI_002</t>
+  </si>
+  <si>
+    <t>BI_003</t>
+  </si>
+  <si>
+    <t>BI_004</t>
+  </si>
+  <si>
+    <t>ATM application will allow an authenticated user to select the Balance Inquiry function</t>
+  </si>
+  <si>
+    <t>ATM application will retrieve the current balance from the simulated account</t>
+  </si>
+  <si>
+    <t>ATM application will display the current account balance on the console</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to return to the main menu after viewing the balance</t>
+  </si>
+  <si>
+    <t>CD_001</t>
+  </si>
+  <si>
+    <t>CD_002</t>
+  </si>
+  <si>
+    <t>CD_003</t>
+  </si>
+  <si>
+    <t>CD_004</t>
+  </si>
+  <si>
+    <t>CD_005</t>
+  </si>
+  <si>
+    <t>CD_006</t>
+  </si>
+  <si>
+    <t>Error handling</t>
+  </si>
+  <si>
+    <t>CD_007</t>
+  </si>
+  <si>
+    <t>BI</t>
+  </si>
+  <si>
+    <t>Balance Inquiry</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Card Insertion</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>Card Deposit</t>
+  </si>
+  <si>
+    <t>ATM application will allow an authenticated user to select the Cash Deposit function</t>
+  </si>
+  <si>
+    <t>ATM application will allow user to enter the amount of cash to deposited</t>
+  </si>
+  <si>
+    <t>ATM application will reject a deposit amount that is zero or negative</t>
+  </si>
+  <si>
+    <t>ATM application will add the valid deposit amount to the user's account balance</t>
+  </si>
+  <si>
+    <t>ATM application will display the updated account balance after a successful deposit</t>
+  </si>
+  <si>
+    <t>ATM application will display an error message when the deposit amount is invalid</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to cancel the deposit before confirming the transaction</t>
+  </si>
+  <si>
+    <t>MT_001</t>
+  </si>
+  <si>
+    <t>Money Transfer</t>
+  </si>
+  <si>
+    <t>MT_002</t>
+  </si>
+  <si>
+    <t>MT_003</t>
+  </si>
+  <si>
+    <t>MT_004</t>
+  </si>
+  <si>
+    <t>MT_005</t>
+  </si>
+  <si>
+    <t>MT_006</t>
+  </si>
+  <si>
+    <t>MT_007</t>
+  </si>
+  <si>
+    <t>MT_008</t>
+  </si>
+  <si>
+    <t>MT_009</t>
+  </si>
+  <si>
+    <t>MT_010</t>
+  </si>
+  <si>
+    <t>MT_011</t>
+  </si>
+  <si>
+    <t>MT_012</t>
+  </si>
+  <si>
+    <t>MT_013</t>
+  </si>
+  <si>
+    <t>ATM application will allow an authenticated user to select the Money Transfer function</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to enter the destination account number</t>
+  </si>
+  <si>
+    <t>ATM application will validate the destination account number before processing the transfer</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to enter the amount to be transferred</t>
+  </si>
+  <si>
+    <t>ATM application will validate the transfer amount before processing the transaction</t>
+  </si>
+  <si>
+    <t>ATM application will verify that the user's account has sufficient balance for the transfer</t>
+  </si>
+  <si>
+    <t>ATM application will transfer the specified amount from the user's account to the destination account when all validations are successful</t>
+  </si>
+  <si>
+    <t>ATM application will deduct the transferred amount from the user's account after a successful transfer</t>
+  </si>
+  <si>
+    <t>ATM application will add the transferred amount to the destination account after a successful transfer</t>
+  </si>
+  <si>
+    <t>ATM application will display the transfer result to the user after processing the transaction</t>
+  </si>
+  <si>
+    <t>ATM application will display an error message when the destination account is invalid</t>
+  </si>
+  <si>
+    <t>ATM application will display an error message when the user's account has insufficient balance</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to cancel the transfer before confirmation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT </t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>Change PIN</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>Transaction History</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>Receipt</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>Card Ejection</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Transaction Cancellation</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>Error Handling</t>
+  </si>
+  <si>
+    <t>Navigation / Main Menu</t>
+  </si>
+  <si>
+    <r>
+      <t>NM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0D0D0D"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>CP_001</t>
+  </si>
+  <si>
+    <t>CP_002</t>
+  </si>
+  <si>
+    <t>CP_003</t>
+  </si>
+  <si>
+    <t>CP_004</t>
+  </si>
+  <si>
+    <t>CP_005</t>
+  </si>
+  <si>
+    <t>CP_006</t>
+  </si>
+  <si>
+    <t>CP_007</t>
+  </si>
+  <si>
+    <t>CP_008</t>
+  </si>
+  <si>
+    <t>TH_001</t>
+  </si>
+  <si>
+    <t>TH_002</t>
+  </si>
+  <si>
+    <t>TH_003</t>
+  </si>
+  <si>
+    <t>TH_004</t>
+  </si>
+  <si>
+    <t>TH_005</t>
+  </si>
+  <si>
+    <t>RC_001</t>
+  </si>
+  <si>
+    <t>RC_002</t>
+  </si>
+  <si>
+    <t>RC_003</t>
+  </si>
+  <si>
+    <t>RC_004</t>
+  </si>
+  <si>
+    <t>RC_005</t>
+  </si>
+  <si>
+    <t>CE_001</t>
+  </si>
+  <si>
+    <t>CE_002</t>
+  </si>
+  <si>
+    <t>CE_003</t>
+  </si>
+  <si>
+    <t>CE_004</t>
+  </si>
+  <si>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>TC_003</t>
+  </si>
+  <si>
+    <t>TC_004</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>EH_001</t>
+  </si>
+  <si>
+    <t>EH_002</t>
+  </si>
+  <si>
+    <t>EH_003</t>
+  </si>
+  <si>
+    <t>EH_004</t>
+  </si>
+  <si>
+    <t>EH_005</t>
+  </si>
+  <si>
+    <t>EH_006</t>
+  </si>
+  <si>
+    <t>NM_001</t>
+  </si>
+  <si>
+    <t>Main Menu</t>
+  </si>
+  <si>
+    <t>NM_002</t>
+  </si>
+  <si>
+    <t>NM_003</t>
+  </si>
+  <si>
+    <t>NM_004</t>
+  </si>
+  <si>
+    <t>NM_005</t>
+  </si>
+  <si>
+    <t>NM_006</t>
+  </si>
+  <si>
+    <t>NM_007</t>
+  </si>
+  <si>
+    <t>ATM application will allow an authenticated user to select the Change PIN function</t>
+  </si>
+  <si>
+    <t>ATM application will require the user to enter the current PIN before changing the PIN</t>
+  </si>
+  <si>
+    <t>ATM application will verify that the entered current PIN is correct</t>
+  </si>
+  <si>
+    <t>ATM application will require the user to confirm the new PIN</t>
+  </si>
+  <si>
+    <t>ATM application will verify that the new PIN and confirmation PIN match</t>
+  </si>
+  <si>
+    <t>ATM application will update the user's PIN when the new PIN is valid and confirmed</t>
+  </si>
+  <si>
+    <t>ATM application will display an error message when the current PIN is incorrect or the new PIN is invalid</t>
+  </si>
+  <si>
+    <t>ATM application will allow an authenticated user to select the Transaction History function</t>
+  </si>
+  <si>
+    <t>ATM application will retrieve the user's transaction history</t>
+  </si>
+  <si>
+    <t>The transaction history will include the transaction type, amount, and transaction result</t>
+  </si>
+  <si>
+    <t>ATM application will display a message when there are no transaction records available</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to request a transaction receipt after a completed transaction</t>
+  </si>
+  <si>
+    <t>The receipt will include the transaction type, transaction amount, transaction result, and account balance when applicable</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to choose whether to receive a receipt after a completed transaction</t>
+  </si>
+  <si>
+    <t>ATM application will not generate a receipt when the user declines the receipt option</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to end the session and request card ejection</t>
+  </si>
+  <si>
+    <t>ATM application will return the card after a transaction is completed or cancelled</t>
+  </si>
+  <si>
+    <t>ATM application will terminate the current session after the card is returned</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to cancel an ongoing transaction before confirmation</t>
+  </si>
+  <si>
+    <t>ATM application will terminate the current transaction when the user selects Cancel</t>
+  </si>
+  <si>
+    <t>ATM application will not modify the account balance when a transaction is cancelled before completion</t>
+  </si>
+  <si>
+    <t>ATM application will display a transaction cancellation message to the user</t>
+  </si>
+  <si>
+    <t>ATM application will return the user to the main menu after a transaction is cancelled</t>
+  </si>
+  <si>
+    <t>ATM application will display an error message when the user enters an invalid option</t>
+  </si>
+  <si>
+    <t>ATM application will display an error message when the entered data does not meet the required format</t>
+  </si>
+  <si>
+    <t>ATM application will not modify account data when a transaction fails</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to retry an operation after a recoverable error</t>
+  </si>
+  <si>
+    <t>ATM application will terminate the current transaction when a critical error prevents the transaction from continuing</t>
+  </si>
+  <si>
+    <t>ATM application will return the user to an appropriate menu after handling a recoverable error</t>
+  </si>
+  <si>
+    <t>ATM application will display the main menu after successful PIN authentication</t>
+  </si>
+  <si>
+    <t>The main menu will provide options for the available ATM functions</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to select a function from the main menu</t>
+  </si>
+  <si>
+    <t>ATM application will navigate the user to the selected function</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to return to the main menu after completing or cancelling a transaction</t>
+  </si>
+  <si>
+    <t>ATM application will display an error message when the user selects an unavailable menu option</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to exit ATM session from the main menu</t>
+  </si>
+  <si>
+    <t>ATM application will allow the user to create a new PIN</t>
+  </si>
+  <si>
+    <t>ATM application will display the user's transaction history</t>
+  </si>
+  <si>
+    <t>ATM application will display the transaction receipt information</t>
+  </si>
+  <si>
+    <t>ATM application will return the card to the user when the session ends</t>
+  </si>
+  <si>
+    <t>Error Message</t>
+  </si>
+  <si>
+    <t>Login</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +714,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0D0D0D"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -175,26 +741,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,135 +1042,833 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.90625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.36328125" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="14.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.90625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.36328125" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A60" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A74" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A76" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A78" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A79" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A81" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A84" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A94" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A98" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A99" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A100" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -614,7 +1879,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736B2B27-1B39-44F2-80F0-178DDCA64A23}">
-  <dimension ref="A3:B4"/>
+  <dimension ref="A3:B15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.26953125" customWidth="1"/>
@@ -637,6 +1902,94 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/C/Project/ATM_Sim/Doc/Requirement.xlsx
+++ b/C/Project/ATM_Sim/Doc/Requirement.xlsx
@@ -1,84 +1,867 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Embedded\C\Project\ATM_Sim\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hienm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67620170-457A-47F5-9354-6ACE4B6C92CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E97779E-0FBF-4314-A52E-C7D1160C5663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C8C8CBD5-AF7B-4CDE-9C87-DEFB2F1262C9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Requirement" sheetId="1" r:id="rId1"/>
-    <sheet name="ReadMe" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>SYS</t>
-  </si>
-  <si>
-    <t>system requirement</t>
-  </si>
-  <si>
-    <t>LOG</t>
-  </si>
-  <si>
-    <t>Login requirement</t>
-  </si>
-  <si>
-    <t>Requirement ID</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Remark</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>SYS_001</t>
-  </si>
-  <si>
-    <t>ATM application not run in a real machine, will be built based on simulation method</t>
-  </si>
-  <si>
-    <t>SYS_002</t>
-  </si>
-  <si>
-    <t>ATM application should be run console, not using UI</t>
-  </si>
-  <si>
-    <t>Source code based on C language,
-without UI support capability</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="199">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Requirement Description</t>
+  </si>
+  <si>
+    <t>Acceptance Criteria</t>
+  </si>
+  <si>
+    <t>Card Insertion</t>
+  </si>
+  <si>
+    <t>System requires the user to enter their account number</t>
+  </si>
+  <si>
+    <t>Display: Please enter your account number:</t>
+  </si>
+  <si>
+    <t>System checks the entered account number in the database and displays the username if exists</t>
+  </si>
+  <si>
+    <t>1. Check if the account exists
+2. Display: Welcome, [Username]!</t>
+  </si>
+  <si>
+    <t>System rejects and shows an error if the account is invalid/not found</t>
+  </si>
+  <si>
+    <t>System moves to the PIN entry step</t>
+  </si>
+  <si>
+    <t>Transition state to Login module</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>System requires the user to enter their 6-digit PIN code</t>
+  </si>
+  <si>
+    <t>Display: Please enter your 6-digit PIN:</t>
+  </si>
+  <si>
+    <t>System masks the entered PIN on the display for security</t>
+  </si>
+  <si>
+    <t>Display characters as asterisks (*) during input</t>
+  </si>
+  <si>
+    <t>System verifies the entered PIN against the account's registered PIN</t>
+  </si>
+  <si>
+    <t>Check input match with stored account PIN</t>
+  </si>
+  <si>
+    <t>System navigates to the Main Menu with correct PIN entry</t>
+  </si>
+  <si>
+    <t>Transition state to Main Menu</t>
+  </si>
+  <si>
+    <t>System shows an error message and allows retry when the PIN is incorrect</t>
+  </si>
+  <si>
+    <t>Display: Incorrect PIN. Please try again.</t>
+  </si>
+  <si>
+    <t>System terminates the session and blocks further attempts after 3 consecutive incorrect PIN entries</t>
+  </si>
+  <si>
+    <t>Terminate session and lock account after 3 failures</t>
+  </si>
+  <si>
+    <t>Main Menu</t>
+  </si>
+  <si>
+    <t>Menu option list: 
+1. Withdraw
+2. Deposit
+3. Transfer
+4. Balance
+5. Change PIN
+6. History
+7. Exit</t>
+  </si>
+  <si>
+    <t>System navigates to the corresponding function</t>
+  </si>
+  <si>
+    <t>Triggers the specific function selected by the user (1 to 7)</t>
+  </si>
+  <si>
+    <t>System displays an error message if the user enters an invalid menu option</t>
+  </si>
+  <si>
+    <t>Display: Invalid option. Please select 1-7</t>
+  </si>
+  <si>
+    <t>Withdrawal</t>
+  </si>
+  <si>
+    <t>System requires the user to select the withdrawal amount</t>
+  </si>
+  <si>
+    <t>Display: Enter amount to withdraw:</t>
+  </si>
+  <si>
+    <t>System validates that the entered amount is positive number</t>
+  </si>
+  <si>
+    <t>If amount &lt;= 0 or invalid format 
+=&gt; Display: Invalid amount. Please try again</t>
+  </si>
+  <si>
+    <t>System checks if the account balance is sufficient</t>
+  </si>
+  <si>
+    <t>Check if Balance &gt;= withdrawal amount</t>
+  </si>
+  <si>
+    <t>System rejects the withdrawal if the balance is insufficient</t>
+  </si>
+  <si>
+    <t>Display: Insufficient balance</t>
+  </si>
+  <si>
+    <t>System updates the database balance and dispenses cash</t>
+  </si>
+  <si>
+    <t>1. Update database balance
+2. Display: Please take your cash
+3. Action: Press Enter after taking cash to continue</t>
+  </si>
+  <si>
+    <t>System displays the success message with the new balance</t>
+  </si>
+  <si>
+    <t>Display: Withdrawal successful! Your new balance is: [Amount]</t>
+  </si>
+  <si>
+    <t>Deposit</t>
+  </si>
+  <si>
+    <t>System requires the user to select the deposit amount</t>
+  </si>
+  <si>
+    <t>Display: Enter amount to deposit:</t>
+  </si>
+  <si>
+    <t>System rejects deposit amounts that are zero or negative</t>
+  </si>
+  <si>
+    <t>If amount &lt;= 0 
+=&gt; Display: Invalid amount. Please try again</t>
+  </si>
+  <si>
+    <t>System requires the user to insert cash into the slot</t>
+  </si>
+  <si>
+    <t>1. Display: Please insert your cash into the slot. 
+2. Action: Press [Enter] when finished</t>
+  </si>
+  <si>
+    <t>System updates balance and shows success message</t>
+  </si>
+  <si>
+    <t>1. Update database balance (Balance = Balance + Amount)
+2. Display: Deposit successful! New balance: [Amount]</t>
+  </si>
+  <si>
+    <t>Money Transfer</t>
+  </si>
+  <si>
+    <t>System requires the user to enter the destination account number</t>
+  </si>
+  <si>
+    <t>Display: Enter destination account:</t>
+  </si>
+  <si>
+    <t>System validates if the destination account exists</t>
+  </si>
+  <si>
+    <t>1. Check database. If not found 
+2. Display: Account not found. Please try again</t>
+  </si>
+  <si>
+    <t>System requires the user to enter the transfer amount</t>
+  </si>
+  <si>
+    <t>Output: Enter transfer amount:</t>
+  </si>
+  <si>
+    <t>System validates if the sender's account has sufficient balance</t>
+  </si>
+  <si>
+    <t>Check if Balance &gt;= transfer amount
+If low =&gt; Output: Insufficient balance</t>
+  </si>
+  <si>
+    <t>Update: Sender Balance = Sender Balance - Amount &amp; Receiver Balance = Receiver Balance + Amount</t>
+  </si>
+  <si>
+    <t>Display: Transfer successful! Your new balance is: [Amount]</t>
+  </si>
+  <si>
+    <t>Balance Inquiry</t>
+  </si>
+  <si>
+    <t>System retrieves and displays the current account balance</t>
+  </si>
+  <si>
+    <t>Display: Your current balance is: [Amount]</t>
+  </si>
+  <si>
+    <t>Change PIN</t>
+  </si>
+  <si>
+    <t>System requires the user to enter the current PIN</t>
+  </si>
+  <si>
+    <t>Display: Enter current PIN:</t>
+  </si>
+  <si>
+    <t>System validates if the entered current PIN matches the database</t>
+  </si>
+  <si>
+    <t>1. Compare input with stored PIN
+2. If incorrect: Display error and handle retry limit (max 3 attempts)</t>
+  </si>
+  <si>
+    <t>System requires the user to enter a new PIN and confirm new PIN(4 to 6 digits)</t>
+  </si>
+  <si>
+    <t>Display: 
+1. Enter new PIN (4-6 digits):
+2. Confirm new PIN:</t>
+  </si>
+  <si>
+    <t>System validates if the new PIN and confirmation match</t>
+  </si>
+  <si>
+    <t>If mismatch =&gt; Display: PINs do not match. Please try again.</t>
+  </si>
+  <si>
+    <t>System updates the PIN in the database on success</t>
+  </si>
+  <si>
+    <t>Display: PIN changed successfully</t>
+  </si>
+  <si>
+    <t>System retrieves and displays the last 5 recent transactions</t>
+  </si>
+  <si>
+    <t>System displays a notification if no transaction history is available</t>
+  </si>
+  <si>
+    <t>Display: No transaction records found</t>
+  </si>
+  <si>
+    <t>Receipt</t>
+  </si>
+  <si>
+    <t>System asks the user whether to display a receipt after a completed transaction</t>
+  </si>
+  <si>
+    <t>Display: Do you want a receipt? (1. Yes/ 2. No)</t>
+  </si>
+  <si>
+    <t>System displays the transaction receipt details if the user chooses Yes (1. Yes)</t>
+  </si>
+  <si>
+    <t>Press 1: 
+1. Display format: Date, Transaction Type, Amount, Balance
+2. Action: Press Enter to proceed</t>
+  </si>
+  <si>
+    <t>System bypasses the receipt and moves to the next step if the user chooses No (2. No)</t>
+  </si>
+  <si>
+    <t>Transaction Cancellation</t>
+  </si>
+  <si>
+    <t>Asks if the user wants another transaction</t>
+  </si>
+  <si>
+    <t>Display: Do you want another transaction? (1. Yes / 2. No)</t>
+  </si>
+  <si>
+    <t>System directs flow based on user's option</t>
+  </si>
+  <si>
+    <t>1. If 1: Back to Main Menu
+2. If 2: Eject card and exit session</t>
+  </si>
+  <si>
+    <t>Card Ejection / Exit</t>
+  </si>
+  <si>
+    <t>Error Handling</t>
+  </si>
+  <si>
+    <t>INS_001</t>
+  </si>
+  <si>
+    <t>INS_002</t>
+  </si>
+  <si>
+    <t>INS_003</t>
+  </si>
+  <si>
+    <t>INS_004</t>
+  </si>
+  <si>
+    <t>AUTH_001</t>
+  </si>
+  <si>
+    <t>AUTH_002</t>
+  </si>
+  <si>
+    <t>AUTH_003</t>
+  </si>
+  <si>
+    <t>AUTH_004</t>
+  </si>
+  <si>
+    <t>AUTH_005</t>
+  </si>
+  <si>
+    <t>AUTH_006</t>
+  </si>
+  <si>
+    <t>MENU_001</t>
+  </si>
+  <si>
+    <t>System displays the main menu options after successful login and requires user choose the option list</t>
+  </si>
+  <si>
+    <t>MENU_002</t>
+  </si>
+  <si>
+    <t>MENU_003</t>
+  </si>
+  <si>
+    <t>WITHDR_001</t>
+  </si>
+  <si>
+    <t>WITHDR_002</t>
+  </si>
+  <si>
+    <t>WITHDR_003</t>
+  </si>
+  <si>
+    <t>WITHDR_004</t>
+  </si>
+  <si>
+    <t>WITHDR_005</t>
+  </si>
+  <si>
+    <t>WITHDR_006</t>
+  </si>
+  <si>
+    <t>TRF_001</t>
+  </si>
+  <si>
+    <t>TRF_002</t>
+  </si>
+  <si>
+    <t>TRF_003</t>
+  </si>
+  <si>
+    <t>TRF_004</t>
+  </si>
+  <si>
+    <t>TRF_005</t>
+  </si>
+  <si>
+    <t>System subtracts the amount from the sender and adds it to the destination account on success</t>
+  </si>
+  <si>
+    <t>TRF_006</t>
+  </si>
+  <si>
+    <t>System shows the successful message after successful transfer</t>
+  </si>
+  <si>
+    <t>BAL_001</t>
+  </si>
+  <si>
+    <t>CPIN_001</t>
+  </si>
+  <si>
+    <t>CPIN_002</t>
+  </si>
+  <si>
+    <t>CPIN_003</t>
+  </si>
+  <si>
+    <t>CPIN_004</t>
+  </si>
+  <si>
+    <t>CPIN_005</t>
+  </si>
+  <si>
+    <t>HIST_001</t>
+  </si>
+  <si>
+    <t>Transaction history</t>
+  </si>
+  <si>
+    <t>HIST_002</t>
+  </si>
+  <si>
+    <t>RCP_001</t>
+  </si>
+  <si>
+    <t>RCP_002</t>
+  </si>
+  <si>
+    <t>RCP_003</t>
+  </si>
+  <si>
+    <t>CONT_001</t>
+  </si>
+  <si>
+    <t>Transaction Loop</t>
+  </si>
+  <si>
+    <t>CONT_002</t>
+  </si>
+  <si>
+    <t>CAN_001</t>
+  </si>
+  <si>
+    <t>System allows the user to cancel an ongoing transaction at any data-entry step before final confirmation</t>
+  </si>
+  <si>
+    <t>Input: User presses a cancel key (e.g., entering C or 0)</t>
+  </si>
+  <si>
+    <t>CAN_002</t>
+  </si>
+  <si>
+    <t>System terminate the current transaction immediately after press cancel key</t>
+  </si>
+  <si>
+    <t>Display: Transaction cancelled by user</t>
+  </si>
+  <si>
+    <t>CAN_003</t>
+  </si>
+  <si>
+    <t>System ensures that the database states remains unchanged and no financial changes are apply when a transactions is aborted</t>
+  </si>
+  <si>
+    <t>CAN_004</t>
+  </si>
+  <si>
+    <t>System redirects the user back to the Main Menu after a cancellation</t>
+  </si>
+  <si>
+    <t>Transition state: Navigate back to Main Menu options</t>
+  </si>
+  <si>
+    <t>EXIT_001</t>
+  </si>
+  <si>
+    <t>System allows the user to exit the session safely from the Main Menu or automatically after choosing not to continue transactions</t>
+  </si>
+  <si>
+    <t>1. Trigger: User selects Exit (e.g., option 7 in Menu) or presses 2 (No) at the transaction loop
+2. Action: Triggers the exit sequence</t>
+  </si>
+  <si>
+    <t>EXIT_002</t>
+  </si>
+  <si>
+    <t>System display "Goodbye message" and resets the flow back to the initial card insertion</t>
+  </si>
+  <si>
+    <t>Display: Thank you. Please take your card.
+When reset the flow: display: Enter your account number</t>
+  </si>
+  <si>
+    <t>EXIT_003</t>
+  </si>
+  <si>
+    <t>Clears all user session data, cache, and status variables from memory</t>
+  </si>
+  <si>
+    <t>ERR_001</t>
+  </si>
+  <si>
+    <t>Handles invalid format inputs (eg: typing letters instead of numbers)</t>
+  </si>
+  <si>
+    <t>1. Triggered when non-numeric characters are entered for numeric fields (PIN, Amount, Account)
+2. Display: Invalid format. Please enter numbers only</t>
+  </si>
+  <si>
+    <t>ERR_002</t>
+  </si>
+  <si>
+    <t>Handles out-of-range or negative numerical values</t>
+  </si>
+  <si>
+    <t>1. Triggered when amount &lt;= 0 or exceeds maximum limit
+2. Display: Invalid amount. Please try again</t>
+  </si>
+  <si>
+    <t>ERR_003</t>
+  </si>
+  <si>
+    <t>Handles invalid menu option selections</t>
+  </si>
+  <si>
+    <t>1. Triggered when the user enters a number outside the allowed range (e.g., choosing 8 when menu is 1-7)
+2. Output: Invalid option. Please select 1-7</t>
+  </si>
+  <si>
+    <t>ERR_004</t>
+  </si>
+  <si>
+    <t>Handles incorrect authentication inputs (PIN or Account)</t>
+  </si>
+  <si>
+    <t>1. Triggered when Account ID is not found or PIN does not match
+2. Display: Account not found or Incorrect PIN
+3. Allow retry up to 3 times before locking/terminating</t>
+  </si>
+  <si>
+    <t>ERR_005</t>
+  </si>
+  <si>
+    <t>Handles insufficient balance during transactions</t>
+  </si>
+  <si>
+    <t>1. Triggered when withdrawal or transfer amount &gt; current balance
+2. Display: Insufficient balance
+3. Return to transaction step or menu without modifying data</t>
+  </si>
+  <si>
+    <t>ERR_006</t>
+  </si>
+  <si>
+    <t>Ensures transaction is rollback all changes to restore initial account balance if a transaction fails</t>
+  </si>
+  <si>
+    <t>1. Triggered if any transaction fails midway
+2. Account balances and database records remain strictly unchanged</t>
+  </si>
+  <si>
+    <t>BAL_002</t>
+  </si>
+  <si>
+    <t>System proceeds to the receipt request after displaying the balance</t>
+  </si>
+  <si>
+    <t>Transition state: Move to Receipt module (RCP_001)</t>
+  </si>
+  <si>
+    <t>CPIN_006</t>
+  </si>
+  <si>
+    <t>System proceeds to the receipt prompt after successfully changing the PIN</t>
+  </si>
+  <si>
+    <t>1. Display Format: Date | Type | Amount | Status 
+2. Press [Enter] to continue</t>
+  </si>
+  <si>
+    <t>HIST_003</t>
+  </si>
+  <si>
+    <t>System proceeds to the receipt prompt after displaying transaction history</t>
+  </si>
+  <si>
+    <t>Press 2:
+1. Skips receipt display and proceeds directly to "another transaction prompt (CONT_001)</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <r>
+      <t>Functional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFB10202"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Performation</t>
+    </r>
+  </si>
+  <si>
+    <t>Non-Functional</t>
+  </si>
+  <si>
+    <t>DEP_001</t>
+  </si>
+  <si>
+    <t>DEP_002</t>
+  </si>
+  <si>
+    <t>DEP_003</t>
+  </si>
+  <si>
+    <t>DEP_004</t>
+  </si>
+  <si>
+    <t>1. Account balances and records are strictly preserved without modification.
+2. Reset temporary session counters (e.g.. incorrect PIN retry attempts = 0).</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Non-existent:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Check DB, if not found 
+=&gt; Display:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Account not found</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2. Invalid format:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Check format (must be numeric, exact length: != 16 ditgits), if failed 
+=&gt; Display: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Invalid format</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3. Unsupported:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Check prefix against allowed list, if not matched 
+=&gt; Display: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Unsupported card</t>
+    </r>
+  </si>
+  <si>
+    <t>Validation method</t>
+  </si>
+  <si>
+    <t>Performation</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Prototyping</t>
+  </si>
+  <si>
+    <t>UAT</t>
+  </si>
+  <si>
+    <t>A/B Testing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Corbel"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF11734B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFB10202"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0A53A8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,7 +872,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -97,17 +880,218 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -134,39 +1118,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -199,9 +1183,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -234,6 +1235,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -295,13 +1313,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -310,6 +1321,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -374,88 +1392,1105 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73396425-2E52-4720-9362-CF64257995AB}">
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="73.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.36328125" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="5" width="47.6328125" customWidth="1"/>
+    <col min="6" max="6" width="25.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C2" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F2" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F3" s="13"/>
+    </row>
+    <row r="4" spans="1:6" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="E4" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F5" s="13"/>
+    </row>
+    <row r="6" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
+      <c r="C6" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13"/>
+    </row>
+    <row r="7" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="13"/>
+    </row>
+    <row r="8" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="13"/>
+    </row>
+    <row r="9" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="1:6" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="13"/>
+    </row>
+    <row r="14" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="13"/>
+    </row>
+    <row r="15" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="13"/>
+    </row>
+    <row r="16" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="13"/>
+    </row>
+    <row r="17" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="13"/>
+    </row>
+    <row r="18" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="1:6" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" spans="1:6" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="13"/>
+    </row>
+    <row r="25" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="13"/>
+    </row>
+    <row r="26" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="13"/>
+    </row>
+    <row r="28" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="13"/>
+    </row>
+    <row r="29" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="13"/>
+    </row>
+    <row r="30" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F31" s="13"/>
+    </row>
+    <row r="32" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="F32" s="13"/>
+    </row>
+    <row r="33" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="13"/>
+    </row>
+    <row r="34" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="13"/>
+    </row>
+    <row r="35" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" s="13"/>
+    </row>
+    <row r="36" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" s="13"/>
+    </row>
+    <row r="38" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="F38" s="13"/>
+    </row>
+    <row r="39" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F39" s="13"/>
+    </row>
+    <row r="40" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" s="13"/>
+    </row>
+    <row r="41" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="F41" s="13"/>
+    </row>
+    <row r="42" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="13"/>
+    </row>
+    <row r="43" spans="1:6" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F43" s="13"/>
+    </row>
+    <row r="44" spans="1:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="12"/>
+      <c r="C44" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="F44" s="13"/>
+    </row>
+    <row r="45" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="13"/>
+    </row>
+    <row r="46" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F46" s="13"/>
+    </row>
+    <row r="47" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F47" s="13"/>
+    </row>
+    <row r="48" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48" s="13"/>
+    </row>
+    <row r="49" spans="1:6" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B49" s="11"/>
+      <c r="C49" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F49" s="13"/>
+    </row>
+    <row r="50" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50" s="12"/>
+      <c r="C50" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" s="13"/>
+    </row>
+    <row r="51" spans="1:6" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="13"/>
+    </row>
+    <row r="52" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" s="11"/>
+      <c r="C52" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F52" s="13"/>
+    </row>
+    <row r="53" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="13"/>
+    </row>
+    <row r="54" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F54" s="13"/>
+    </row>
+    <row r="55" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F55" s="13"/>
+    </row>
+    <row r="56" spans="1:6" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" s="11"/>
+      <c r="C56" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F56" s="13"/>
+    </row>
+    <row r="57" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" s="11"/>
+      <c r="C57" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F57" s="13"/>
+    </row>
+    <row r="58" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="11"/>
+      <c r="C58" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F58" s="13"/>
+    </row>
+    <row r="59" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="12"/>
+      <c r="C59" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F59" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B54:B59"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B38"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="B51:B53"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E32" location="Sheet1!D42:E42" display="Transition state: Move to Receipt module (RCP_001)" xr:uid="{B6E8ADDA-7869-4063-B5A3-AE8BF4AB5F40}"/>
+    <hyperlink ref="E38" location="Sheet1!D42:E42" display="Transition state: Move to Receipt module (RCP_001)" xr:uid="{0B4EA2E9-1F1D-4CC2-AEF0-FD2C3883A229}"/>
+    <hyperlink ref="E41" location="Sheet1!D42:E42" display="Transition state: Move to Receipt module (RCP_001)" xr:uid="{AD0C591B-7D97-4347-8DBA-9C1CB685DA9C}"/>
+    <hyperlink ref="E44" location="Sheet1!D45:E45" display="Sheet1!D45:E45" xr:uid="{C55F6207-6F64-49FC-B0B3-A852F05ACCD3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{50A6876A-AF12-49ED-81C7-AC36FD46AF52}">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$1:$A$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C59</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5696762B-4D93-418C-B3AC-1475C0B1953B}">
+          <x14:formula1>
+            <xm:f>Sheet2!$B$1:$B$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F59</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736B2B27-1B39-44F2-80F0-178DDCA64A23}">
-  <dimension ref="A3:B4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B7007E-B681-4F10-B6E7-57E2CAEA2E4F}">
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" t="s">
+        <v>196</v>
+      </c>
+    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
